--- a/output/贵州茅台(600519)_年报财务数据.xlsx
+++ b/output/贵州茅台(600519)_年报财务数据.xlsx
@@ -8,19 +8,13 @@
   </bookViews>
   <sheets>
     <sheet name="资产负债表_2023年" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="资产负债表_2022年" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="利润表_2023年" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="利润表_2022年" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="现金流量表_2023年" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="现金流量表_2022年" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="利润表_2023年" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="现金流量表_2023年" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'资产负债表_2023年'!$A$1:$BE$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'资产负债表_2022年'!$A$1:$BE$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'利润表_2023年'!$A$1:$AT$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'利润表_2022年'!$A$1:$AT$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'现金流量表_2023年'!$A$1:$AV$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'现金流量表_2022年'!$A$1:$AV$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'利润表_2023年'!$A$1:$AT$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'现金流量表_2023年'!$A$1:$AV$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -961,498 +955,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="18" customWidth="1" min="28" max="28"/>
-    <col width="18" customWidth="1" min="29" max="29"/>
-    <col width="18" customWidth="1" min="30" max="30"/>
-    <col width="18" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="18" customWidth="1" min="33" max="33"/>
-    <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="24.2" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
-    <col width="18" customWidth="1" min="39" max="39"/>
-    <col width="18" customWidth="1" min="40" max="40"/>
-    <col width="18" customWidth="1" min="41" max="41"/>
-    <col width="14" customWidth="1" min="42" max="42"/>
-    <col width="14" customWidth="1" min="43" max="43"/>
-    <col width="18" customWidth="1" min="44" max="44"/>
-    <col width="24.2" customWidth="1" min="45" max="45"/>
-    <col width="14" customWidth="1" min="46" max="46"/>
-    <col width="14" customWidth="1" min="47" max="47"/>
-    <col width="14" customWidth="1" min="48" max="48"/>
-    <col width="14" customWidth="1" min="49" max="49"/>
-    <col width="14" customWidth="1" min="50" max="50"/>
-    <col width="14" customWidth="1" min="51" max="51"/>
-    <col width="14" customWidth="1" min="52" max="52"/>
-    <col width="14" customWidth="1" min="53" max="53"/>
-    <col width="18" customWidth="1" min="54" max="54"/>
-    <col width="18" customWidth="1" min="55" max="55"/>
-    <col width="14" customWidth="1" min="56" max="56"/>
-    <col width="14" customWidth="1" min="57" max="57"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>证券代码</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>股票代码</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>行业代码</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>机构代码</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>证券简称</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>行业名称</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>交易市场</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>证券类型代码</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>交易市场代码</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>日期类型代码</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>报告类型代码</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>数据状态</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>公告日期</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>报告日期</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>资产总计</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>固定资产</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>货币资金</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>货币资金增长率(%)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>应收账款</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>应收账款同比</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>存货</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>存货增长率(%)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>负债合计</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>应付账款</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>应付账款同比</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>预收款项</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>预收款项同比</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>股东权益合计</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>股东权益合计同比</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>资产总计同比</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>负债合计同比</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>流动比率</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>资产负债率</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>现金及存放央行款项</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>现金及存放央行款项同比</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>发放贷款及垫款</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>发放贷款及垫款同比</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>可供出售金融资产</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>可供出售金融资产同比</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>向央行借款</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>向央行借款同比</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>吸收存款</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>吸收存款同比</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>卖出回购金融资产款</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>卖出回购金融资产款同比</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>结算备付金</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>结算备付金同比</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>拆入资金</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>拆入资金同比</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>代理买卖证券款</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>代理买卖证券款同比</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>应收保费</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>应收保费同比</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>短期借款</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>短期借款同比</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>预收保费</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>预收保费同比</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>600519.SH</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>600519</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>1277</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>10002602</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>贵州茅台</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>白酒Ⅱ</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>shzb</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>58001001</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>69001001001</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>2024-04-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>2022-12-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>254500826096.02</v>
-      </c>
-      <c r="P2" s="3" t="n">
-        <v>19742622547.86</v>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>58274318733.23</v>
-      </c>
-      <c r="R2" s="2" t="n">
-        <v>12.4764422556</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>20937144</v>
-      </c>
-      <c r="T2" s="2" t="n"/>
-      <c r="U2" s="2" t="n">
-        <v>38824374236.24</v>
-      </c>
-      <c r="V2" s="2" t="n">
-        <v>16.2602556977</v>
-      </c>
-      <c r="W2" s="3" t="n">
-        <v>49562744832.16</v>
-      </c>
-      <c r="X2" s="2" t="n">
-        <v>2408371053.69</v>
-      </c>
-      <c r="Y2" s="2" t="n">
-        <v>19.8294414589</v>
-      </c>
-      <c r="Z2" s="2" t="n"/>
-      <c r="AA2" s="2" t="n"/>
-      <c r="AB2" s="3" t="n">
-        <v>204938081263.86</v>
-      </c>
-      <c r="AC2" s="3" t="n">
-        <v>4.0519270842</v>
-      </c>
-      <c r="AD2" s="3" t="n">
-        <v>-0.3148472968</v>
-      </c>
-      <c r="AE2" s="3" t="n">
-        <v>-15.1356596998</v>
-      </c>
-      <c r="AF2" s="2" t="n">
-        <v>441.4725020116</v>
-      </c>
-      <c r="AG2" s="3" t="n">
-        <v>19.4744927128</v>
-      </c>
-      <c r="AH2" s="4" t="n"/>
-      <c r="AI2" s="4" t="n"/>
-      <c r="AJ2" s="2" t="n"/>
-      <c r="AK2" s="2" t="n"/>
-      <c r="AL2" s="4" t="n"/>
-      <c r="AM2" s="4" t="n"/>
-      <c r="AN2" s="4" t="n"/>
-      <c r="AO2" s="4" t="n"/>
-      <c r="AP2" s="2" t="n"/>
-      <c r="AQ2" s="2" t="n"/>
-      <c r="AR2" s="4" t="n"/>
-      <c r="AS2" s="4" t="n"/>
-      <c r="AT2" s="2" t="n"/>
-      <c r="AU2" s="2" t="n"/>
-      <c r="AV2" s="2" t="n"/>
-      <c r="AW2" s="2" t="n"/>
-      <c r="AX2" s="2" t="n"/>
-      <c r="AY2" s="2" t="n"/>
-      <c r="AZ2" s="2" t="n"/>
-      <c r="BA2" s="2" t="n"/>
-      <c r="BB2" s="4" t="n"/>
-      <c r="BC2" s="4" t="n"/>
-      <c r="BD2" s="2" t="n"/>
-      <c r="BE2" s="2" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:BE2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:AT2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1876,436 +1378,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AT2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="26.4" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="18" customWidth="1" min="24" max="24"/>
-    <col width="18" customWidth="1" min="25" max="25"/>
-    <col width="18" customWidth="1" min="26" max="26"/>
-    <col width="18" customWidth="1" min="27" max="27"/>
-    <col width="18" customWidth="1" min="28" max="28"/>
-    <col width="18" customWidth="1" min="29" max="29"/>
-    <col width="18" customWidth="1" min="30" max="30"/>
-    <col width="18" customWidth="1" min="31" max="31"/>
-    <col width="24.2" customWidth="1" min="32" max="32"/>
-    <col width="18" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="28.6" customWidth="1" min="35" max="35"/>
-    <col width="18" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="18" customWidth="1" min="39" max="39"/>
-    <col width="14" customWidth="1" min="40" max="40"/>
-    <col width="18" customWidth="1" min="41" max="41"/>
-    <col width="18" customWidth="1" min="42" max="42"/>
-    <col width="18" customWidth="1" min="43" max="43"/>
-    <col width="18" customWidth="1" min="44" max="44"/>
-    <col width="18" customWidth="1" min="45" max="45"/>
-    <col width="26.4" customWidth="1" min="46" max="46"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>证券代码</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>股票代码</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>行业代码</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>机构代码</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>证券简称</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>行业名称</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>交易市场</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>证券类型代码</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>交易市场代码</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>日期类型代码</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>报告类型代码</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>数据状态</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>公告日期</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>报告日期</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>归属于母公司股东的净利润</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>营业总收入</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>营业总成本</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>营业总成本同比</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>营业成本</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>营业支出</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>营业支出同比</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>销售费用</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>管理费用</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>财务费用</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>营业利润</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>利润总额</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>所得税费用</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>营业收入</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>利息净收入</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>利息净收入同比</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>手续费及佣金净收入</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>手续费及佣金净收入同比</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>税金及附加</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>业务及管理费(银行)</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>手续费及佣金净收入(计算)</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>利息净收入(计算)</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>已赚保费</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>已赚保费同比</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>投资收益</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>退保金</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>赔付支出</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>营业总收入同比</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>营业利润同比</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>归属母公司净利润同比</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>扣非归属母公司净利润</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>扣非归属母公司净利润同比</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>600519.SH</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>600519</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>1277</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>10002602</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>贵州茅台</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>白酒Ⅱ</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>shzb</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>58001001</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>69001001001</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>2024-04-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>2022-12-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>62717467870.12</v>
-      </c>
-      <c r="P2" s="3" t="n">
-        <v>127553959355.97</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>39748309616.85</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>14.2951407303</v>
-      </c>
-      <c r="S2" s="3" t="n">
-        <v>10093468616.63</v>
-      </c>
-      <c r="T2" s="3" t="n">
-        <v>10093468616.63</v>
-      </c>
-      <c r="U2" s="3" t="n">
-        <v>12.3571648678</v>
-      </c>
-      <c r="V2" s="3" t="n">
-        <v>3297724190.94</v>
-      </c>
-      <c r="W2" s="3" t="n">
-        <v>9012191073.629999</v>
-      </c>
-      <c r="X2" s="3" t="n">
-        <v>-1391805826.72</v>
-      </c>
-      <c r="Y2" s="3" t="n">
-        <v>87879521782.39</v>
-      </c>
-      <c r="Z2" s="3" t="n">
-        <v>87701489748.17999</v>
-      </c>
-      <c r="AA2" s="3" t="n">
-        <v>22325449790.3</v>
-      </c>
-      <c r="AB2" s="4" t="n"/>
-      <c r="AC2" s="3" t="n">
-        <v>3348531377.74</v>
-      </c>
-      <c r="AD2" s="4" t="n"/>
-      <c r="AE2" s="3" t="n">
-        <v>-143141.51</v>
-      </c>
-      <c r="AF2" s="4" t="n"/>
-      <c r="AG2" s="3" t="n">
-        <v>18495818534.22</v>
-      </c>
-      <c r="AH2" s="2" t="n"/>
-      <c r="AI2" s="3" t="n">
-        <v>-143141.51</v>
-      </c>
-      <c r="AJ2" s="3" t="n">
-        <v>3348531377.74</v>
-      </c>
-      <c r="AK2" s="2" t="n"/>
-      <c r="AL2" s="2" t="n"/>
-      <c r="AM2" s="4" t="n"/>
-      <c r="AN2" s="2" t="n"/>
-      <c r="AO2" s="4" t="n"/>
-      <c r="AP2" s="3" t="n">
-        <v>16.5256474801</v>
-      </c>
-      <c r="AQ2" s="3" t="n">
-        <v>17.563192390929</v>
-      </c>
-      <c r="AR2" s="3" t="n">
-        <v>19.55</v>
-      </c>
-      <c r="AS2" s="3" t="n">
-        <v>62792896829.57</v>
-      </c>
-      <c r="AT2" s="3" t="n">
-        <v>19.47506898896</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:AT2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2732,433 +1805,4 @@
   <autoFilter ref="A1:AV2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AV2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="28.6" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="30.8" customWidth="1" min="17" max="17"/>
-    <col width="33" customWidth="1" min="18" max="18"/>
-    <col width="33" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="28.6" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="24.2" customWidth="1" min="23" max="23"/>
-    <col width="28.6" customWidth="1" min="24" max="24"/>
-    <col width="48.40000000000001" customWidth="1" min="25" max="25"/>
-    <col width="28.6" customWidth="1" min="26" max="26"/>
-    <col width="28.6" customWidth="1" min="27" max="27"/>
-    <col width="18" customWidth="1" min="28" max="28"/>
-    <col width="26.4" customWidth="1" min="29" max="29"/>
-    <col width="30.8" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="28.6" customWidth="1" min="33" max="33"/>
-    <col width="24.2" customWidth="1" min="34" max="34"/>
-    <col width="24.2" customWidth="1" min="35" max="35"/>
-    <col width="28.6" customWidth="1" min="36" max="36"/>
-    <col width="26.4" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
-    <col width="18" customWidth="1" min="39" max="39"/>
-    <col width="18" customWidth="1" min="40" max="40"/>
-    <col width="26.4" customWidth="1" min="41" max="41"/>
-    <col width="18" customWidth="1" min="42" max="42"/>
-    <col width="26.4" customWidth="1" min="43" max="43"/>
-    <col width="18" customWidth="1" min="44" max="44"/>
-    <col width="14" customWidth="1" min="45" max="45"/>
-    <col width="24.2" customWidth="1" min="46" max="46"/>
-    <col width="24.2" customWidth="1" min="47" max="47"/>
-    <col width="28.6" customWidth="1" min="48" max="48"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>证券代码</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>股票代码</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>行业代码</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>机构代码</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>证券简称</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>行业名称</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>交易市场</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>证券类型代码</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>交易市场代码</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>日期类型代码</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>报告类型代码</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>数据状态</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>公告日期</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>报告日期</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>经营活动产生的现金流量净额</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>经营活动现金流同比</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>销售商品、提供劳务收到的现金</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>销售商品提供劳务收到的现金同比</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>支付给职工以及为职工支付的现金</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>支付给职工的现金同比</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>投资活动产生的现金流量净额</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>投资活动现金流同比</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>取得投资收益收到的现金</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>取得投资收益收到的现金同比</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>购建固定资产无形资产和其他长期资产支付的现金</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>购建长期资产支付的现金同比</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>筹资活动产生的现金流量净额</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>筹资活动现金流同比</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>现金及现金等价物净增加额</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>现金及现金等价物净增加额同比</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>客户存款净增加额</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>客户存款净增加额同比</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>存放同业和拆出资金净增加额</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>存放同业和拆出资金同比</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>发放贷款及垫款净增加额</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>发放贷款及垫款净增加额同比</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>收取利息和手续费净增加额</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>收取利息和手续费同比</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>投资支付的现金</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>投资支付的现金同比</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>期初现金及现金等价物余额</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>期初现金同比</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>期末现金及现金等价物余额</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>期末现金同比</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>收到原保险合同保费</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>收到原保险合同保费同比</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>支付原保险合同赔付款项</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>支付原保险合同赔付款项同比</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>600519.SH</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>600519</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>1277</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>10002602</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>贵州茅台</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>白酒Ⅱ</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>shzb</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>58001001</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>69001001001</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>2024-04-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>2022-12-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>36698595830.03</v>
-      </c>
-      <c r="P2" s="3" t="n">
-        <v>139.7411000006</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>140691678592</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>535.7264898755</v>
-      </c>
-      <c r="S2" s="3" t="n">
-        <v>11752241598.62</v>
-      </c>
-      <c r="T2" s="3" t="n">
-        <v>44.7502453792</v>
-      </c>
-      <c r="U2" s="3" t="n">
-        <v>-5536826334.9</v>
-      </c>
-      <c r="V2" s="3" t="n">
-        <v>-21.083155501</v>
-      </c>
-      <c r="W2" s="3" t="n">
-        <v>5880000</v>
-      </c>
-      <c r="X2" s="3" t="n">
-        <v>0.0223898939</v>
-      </c>
-      <c r="Y2" s="3" t="n">
-        <v>5306546416.54</v>
-      </c>
-      <c r="Z2" s="3" t="n">
-        <v>20.2062944557</v>
-      </c>
-      <c r="AA2" s="3" t="n">
-        <v>-57424528979.83</v>
-      </c>
-      <c r="AB2" s="3" t="n">
-        <v>-218.6614137452</v>
-      </c>
-      <c r="AC2" s="3" t="n">
-        <v>-26261848396.69</v>
-      </c>
-      <c r="AD2" s="3" t="n">
-        <v>-182.3253822379</v>
-      </c>
-      <c r="AE2" s="2" t="n"/>
-      <c r="AF2" s="2" t="n"/>
-      <c r="AG2" s="2" t="n"/>
-      <c r="AH2" s="2" t="n"/>
-      <c r="AI2" s="2" t="n"/>
-      <c r="AJ2" s="2" t="n"/>
-      <c r="AK2" s="4" t="n"/>
-      <c r="AL2" s="4" t="n"/>
-      <c r="AM2" s="4" t="n"/>
-      <c r="AN2" s="4" t="n"/>
-      <c r="AO2" s="4" t="n"/>
-      <c r="AP2" s="4" t="n"/>
-      <c r="AQ2" s="4" t="n"/>
-      <c r="AR2" s="4" t="n"/>
-      <c r="AS2" s="2" t="n"/>
-      <c r="AT2" s="2" t="n"/>
-      <c r="AU2" s="2" t="n"/>
-      <c r="AV2" s="2" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:AV2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/output/贵州茅台(600519)_年报财务数据.xlsx
+++ b/output/贵州茅台(600519)_年报财务数据.xlsx
@@ -10,11 +10,17 @@
     <sheet name="资产负债表_2023年" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="利润表_2023年" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="现金流量表_2023年" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="行业均值_资产负债表_2023年" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="行业均值_利润表_2023年" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="行业均值_现金流量表_2023年" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'资产负债表_2023年'!$A$1:$BE$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'利润表_2023年'!$A$1:$AT$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'现金流量表_2023年'!$A$1:$AV$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'行业均值_资产负债表_2023年'!$A$1:$AA$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'行业均值_利润表_2023年'!$A$1:$AC$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'行业均值_现金流量表_2023年'!$A$1:$X$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1805,4 +1811,787 @@
   <autoFilter ref="A1:AV2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AA2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>货币资金</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>预收款项同比</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>存货增长率(%)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>流动比率</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>资产总计</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>证券类型代码</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>交易市场代码</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>应付账款</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>股东权益合计同比</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>资产负债率</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>行业代码</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>固定资产</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>资产总计同比</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>日期类型代码</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>应收账款</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>报告类型代码</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>数据状态</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>股东权益合计</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>机构代码</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>存货</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>股票代码</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>预收款项</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>负债合计同比</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>负债合计</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>货币资金增长率(%)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>应收账款同比</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>应付账款同比</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>11364518281.66895</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>0.7802370313714292</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>10.31687553015789</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>249.1896468610368</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>25951197573.92947</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>58001001</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>69001001422.1579</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>1291895541.872632</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>12.2816066822</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>35.57002394773158</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>1277</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>2357200701.812632</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>10.51367633145789</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>41040929.01736841</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>18399982815.61421</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>10140394.63157895</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>5404261454.427368</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>348823.2631578947</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>4420767.855</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>7.982423231157895</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>7551214758.315263</v>
+      </c>
+      <c r="Y2" s="2" t="n">
+        <v>5.107648534626316</v>
+      </c>
+      <c r="Z2" s="2" t="n">
+        <v>4.008804946531578</v>
+      </c>
+      <c r="AA2" s="2" t="n">
+        <v>19.29717077870527</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:AA2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AC2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="26.4" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
+    <col width="26.4" customWidth="1" min="26" max="26"/>
+    <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="18" customWidth="1" min="29" max="29"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>营业利润</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>扣非归属母公司净利润</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>营业利润同比</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>所得税费用</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>营业成本</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>营业总收入同比</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>归属母公司净利润同比</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>证券类型代码</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>交易市场代码</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>销售费用</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>行业代码</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>财务费用</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>日期类型代码</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>营业总收入</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>营业支出同比</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>营业总成本</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>报告类型代码</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>归属于母公司股东的净利润</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>营业总成本同比</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>数据状态</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>营业支出</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>机构代码</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>股票代码</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>利息净收入(计算)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>扣非归属母公司净利润同比</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>利息净收入</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>税金及附加</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>利润总额</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>5788112012.579473</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>4178302030.815263</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>22.78820841577721</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>1468017296.784737</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>3460547309.429473</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>16.96952973401579</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>13.86925173043879</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>58001001</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>69001001422.1579</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>1973109847.771053</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>1277</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>-209425068.1452632</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>688639996.7036842</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>13768894216.41526</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>13.14833888130526</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>8089479901.920526</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>4231814336.089474</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>15.44804413074211</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>3460547309.429473</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>10140394.63157895</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>348823.2631578947</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>2393587.76</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>10.58490893510216</v>
+      </c>
+      <c r="AA2" s="3" t="n">
+        <v>2393587.76</v>
+      </c>
+      <c r="AB2" s="3" t="n">
+        <v>2099332094.547895</v>
+      </c>
+      <c r="AC2" s="3" t="n">
+        <v>5779857513.955263</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:AC2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30.8" customWidth="1" min="1" max="1"/>
+    <col width="24.2" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="28.6" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="28.6" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="28.6" customWidth="1" min="18" max="18"/>
+    <col width="30.8" customWidth="1" min="19" max="19"/>
+    <col width="26.4" customWidth="1" min="20" max="20"/>
+    <col width="28.6" customWidth="1" min="21" max="21"/>
+    <col width="33" customWidth="1" min="22" max="22"/>
+    <col width="28.6" customWidth="1" min="23" max="23"/>
+    <col width="48.40000000000001" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>现金及现金等价物净增加额同比</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>取得投资收益收到的现金</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>经营活动现金流同比</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>销售商品提供劳务收到的现金同比</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>证券类型代码</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>交易市场代码</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>投资活动现金流同比</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>支付给职工的现金同比</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>筹资活动现金流同比</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>行业代码</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>购建长期资产支付的现金同比</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>日期类型代码</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>投资活动产生的现金流量净额</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>报告类型代码</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>数据状态</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>机构代码</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>股票代码</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>筹资活动产生的现金流量净额</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>销售商品、提供劳务收到的现金</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>现金及现金等价物净增加额</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>取得投资收益收到的现金同比</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>支付给职工以及为职工支付的现金</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>经营活动产生的现金流量净额</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>购建固定资产无形资产和其他长期资产支付的现金</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>102.4475706614737</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>78759553.42846154</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>260.3287390580948</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>2500.6102734669</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>58001001</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>69001001422.1579</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>-113.8771015292947</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>434.2176754814632</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>-141.2622578926421</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>1277</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>150.5443427809</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>-927496479.3615789</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>10140394.63157895</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>348823.2631578947</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>-1881364364.661052</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>15282267086.3021</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>1404357889.721579</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>6.679447812284615</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>1451393607.469474</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>4213086286.663158</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>795397807.2931579</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>